--- a/BrancheIntermediare/ig/mappingAdministrativeGender.xlsx
+++ b/BrancheIntermediare/ig/mappingAdministrativeGender.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T10:04:13+00:00</t>
+    <t>2025-10-03T09:50:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
